--- a/data/trans_orig/IP07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general percibida por adulto en 2007 (tasa de respuesta: 99,81%)</t>
+          <t>Menores según su salud general percibida por el adulto en 2007 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>20919</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>16048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30007</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29905</t>
+          <t>29634</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47150</t>
+          <t>46991</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31562</t>
+          <t>31676</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46847</t>
+          <t>46820</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28562</t>
+          <t>28267</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43297</t>
+          <t>43015</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64037</t>
+          <t>63148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84386</t>
+          <t>85596</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24881</t>
+          <t>24775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39658</t>
+          <t>40098</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>17620</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30034</t>
+          <t>30731</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>45532</t>
+          <t>45863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64440</t>
+          <t>64931</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,67%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>10399</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>12894</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27094</t>
+          <t>26589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76624</t>
+          <t>75935</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103241</t>
+          <t>102653</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84607</t>
+          <t>84700</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113977</t>
+          <t>112112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>169014</t>
+          <t>168923</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>208118</t>
+          <t>207777</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>185730</t>
+          <t>187143</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>217911</t>
+          <t>220557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>213583</t>
+          <t>215862</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>249120</t>
+          <t>250192</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>410511</t>
+          <t>411553</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>458710</t>
+          <t>458901</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,47%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104221</t>
+          <t>104142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131923</t>
+          <t>132244</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114038</t>
+          <t>113060</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>144167</t>
+          <t>145037</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>224740</t>
+          <t>225840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>266701</t>
+          <t>267885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27686</t>
+          <t>27984</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45224</t>
+          <t>46022</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>14728</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29197</t>
+          <t>28808</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45801</t>
+          <t>46927</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>68976</t>
+          <t>69120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73304</t>
+          <t>71696</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94790</t>
+          <t>93204</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64177</t>
+          <t>64618</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84293</t>
+          <t>84848</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>143578</t>
+          <t>143789</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>173873</t>
+          <t>174177</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,54%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44289</t>
+          <t>45236</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63777</t>
+          <t>64758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47197</t>
+          <t>47357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66271</t>
+          <t>65931</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97573</t>
+          <t>96873</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124873</t>
+          <t>125097</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15616</t>
+          <t>14777</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29491</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22954</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41087</t>
+          <t>40731</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>124187</t>
+          <t>124240</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>157613</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126146</t>
+          <t>125731</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>160223</t>
+          <t>158638</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>259952</t>
+          <t>261439</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>306875</t>
+          <t>309191</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>303473</t>
+          <t>307527</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>344318</t>
+          <t>347175</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>323042</t>
+          <t>321453</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>364516</t>
+          <t>365469</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>637558</t>
+          <t>635021</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>699034</t>
+          <t>696014</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,71%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>184527</t>
+          <t>185137</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>221686</t>
+          <t>223318</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>188115</t>
+          <t>189128</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>227984</t>
+          <t>229970</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>386501</t>
+          <t>385730</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>440109</t>
+          <t>442634</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general percibida por adulto en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Menores según su salud general percibida por el adulto en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9053</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>21202</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35317</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15687</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28701</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39678</t>
+          <t>40221</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59995</t>
+          <t>59845</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35213</t>
+          <t>35461</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50304</t>
+          <t>51580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35582</t>
+          <t>36156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51609</t>
+          <t>51658</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75554</t>
+          <t>76950</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97915</t>
+          <t>98542</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,45%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13040</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25629</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23539</t>
+          <t>23309</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26505</t>
+          <t>26669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44023</t>
+          <t>43770</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20064</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16372</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31677</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79285</t>
+          <t>78933</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>107675</t>
+          <t>106452</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>97794</t>
+          <t>97157</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>129039</t>
+          <t>128559</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>183107</t>
+          <t>184093</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>225436</t>
+          <t>224174</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205558</t>
+          <t>205365</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>241806</t>
+          <t>240510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218205</t>
+          <t>217963</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>255867</t>
+          <t>254565</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>434333</t>
+          <t>434491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>484961</t>
+          <t>488033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,79%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109511</t>
+          <t>109641</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140241</t>
+          <t>140240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112432</t>
+          <t>114655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145786</t>
+          <t>145404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>232952</t>
+          <t>232143</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>276540</t>
+          <t>274962</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>792</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30815</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48541</t>
+          <t>49577</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27882</t>
+          <t>28377</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46465</t>
+          <t>47126</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63519</t>
+          <t>64356</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>88701</t>
+          <t>90019</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78241</t>
+          <t>77465</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99756</t>
+          <t>98733</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78886</t>
+          <t>79178</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100604</t>
+          <t>101081</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>162696</t>
+          <t>164048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>192308</t>
+          <t>193560</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29289</t>
+          <t>29302</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46915</t>
+          <t>46878</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35246</t>
+          <t>34344</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54271</t>
+          <t>53377</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68803</t>
+          <t>68547</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93953</t>
+          <t>93062</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>21987</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22937</t>
+          <t>22333</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41246</t>
+          <t>39837</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>142190</t>
+          <t>141628</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>177439</t>
+          <t>177477</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>153408</t>
+          <t>153342</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>191301</t>
+          <t>189918</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>304767</t>
+          <t>304294</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>356708</t>
+          <t>357195</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>332218</t>
+          <t>332494</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>375280</t>
+          <t>376184</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>347947</t>
+          <t>347991</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>394435</t>
+          <t>392673</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>692592</t>
+          <t>690824</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>756969</t>
+          <t>752230</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,58%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161351</t>
+          <t>160800</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>199092</t>
+          <t>199070</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>168408</t>
+          <t>167097</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>208670</t>
+          <t>207023</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>343119</t>
+          <t>342994</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>396870</t>
+          <t>397033</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general percibida por adulto en 2016 (tasa de respuesta: 99,48%)</t>
+          <t>Menores según su salud general percibida por el adulto en 2016 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>531</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13319</t>
+          <t>13959</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27150</t>
+          <t>26984</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13592</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25125</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>18303</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31426</t>
+          <t>31012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34466</t>
+          <t>34053</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52082</t>
+          <t>51857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22524</t>
+          <t>22124</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34752</t>
+          <t>35143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>25987</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39044</t>
+          <t>38593</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52074</t>
+          <t>51317</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70782</t>
+          <t>69335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>54,17%</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14745</t>
+          <t>14309</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>16044</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>12577</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25993</t>
+          <t>26078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34425</t>
+          <t>34241</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54864</t>
+          <t>55605</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43975</t>
+          <t>43908</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66662</t>
+          <t>67118</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84568</t>
+          <t>84380</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115530</t>
+          <t>114792</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153973</t>
+          <t>153520</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187996</t>
+          <t>187726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>164126</t>
+          <t>163215</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>197273</t>
+          <t>197856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>329798</t>
+          <t>326017</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>375724</t>
+          <t>377597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225728</t>
+          <t>227757</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>261466</t>
+          <t>262711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223075</t>
+          <t>222470</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>259346</t>
+          <t>257551</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>456876</t>
+          <t>456994</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>505772</t>
+          <t>509558</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,33%</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30719</t>
+          <t>30549</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33323</t>
+          <t>32608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36069</t>
+          <t>36512</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57722</t>
+          <t>58221</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63464</t>
+          <t>63780</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85011</t>
+          <t>84744</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58053</t>
+          <t>57921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79532</t>
+          <t>79792</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128478</t>
+          <t>126483</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>158688</t>
+          <t>156867</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63542</t>
+          <t>62957</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84036</t>
+          <t>84168</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80059</t>
+          <t>81327</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103264</t>
+          <t>104388</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>149993</t>
+          <t>151407</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>181124</t>
+          <t>182890</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>51,05%</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18955</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>21270</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35510</t>
+          <t>35043</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>63457</t>
+          <t>63945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>89609</t>
+          <t>90433</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>74469</t>
+          <t>74828</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103999</t>
+          <t>104898</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>145624</t>
+          <t>146596</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>183776</t>
+          <t>185168</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>243966</t>
+          <t>243401</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>284085</t>
+          <t>283171</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>252359</t>
+          <t>253269</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>293813</t>
+          <t>295461</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>508615</t>
+          <t>507798</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>570362</t>
+          <t>566974</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>324372</t>
+          <t>327234</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>367000</t>
+          <t>367850</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>342881</t>
+          <t>339023</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>385964</t>
+          <t>383060</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>678899</t>
+          <t>678694</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>741576</t>
+          <t>741288</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general percibida por adulto en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según su salud general percibida por el adulto en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23503</t>
+          <t>23974</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28607</t>
+          <t>26873</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15869</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19080</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>15428</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31048</t>
+          <t>31209</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26250</t>
+          <t>25527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32665</t>
+          <t>31309</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31901</t>
+          <t>32239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54215</t>
+          <t>52958</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28477</t>
+          <t>28462</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29419</t>
+          <t>29528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51507</t>
+          <t>50692</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18717</t>
+          <t>18366</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12294</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27295</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65352</t>
+          <t>65569</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97334</t>
+          <t>98342</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94373</t>
+          <t>93037</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>140680</t>
+          <t>140249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>170689</t>
+          <t>169504</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>232294</t>
+          <t>229055</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154406</t>
+          <t>157693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>219115</t>
+          <t>216788</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>213714</t>
+          <t>214086</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>262710</t>
+          <t>259949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>388837</t>
+          <t>390984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>468267</t>
+          <t>468222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143552</t>
+          <t>143236</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>234385</t>
+          <t>230422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136635</t>
+          <t>135195</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180781</t>
+          <t>177929</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>293079</t>
+          <t>292071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>392301</t>
+          <t>386695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>12163</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28258</t>
+          <t>29145</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46195</t>
+          <t>45871</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29755</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52944</t>
+          <t>50550</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63185</t>
+          <t>63387</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91142</t>
+          <t>91062</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48004</t>
+          <t>47061</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67277</t>
+          <t>67565</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62215</t>
+          <t>60756</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87606</t>
+          <t>86930</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117736</t>
+          <t>114689</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148108</t>
+          <t>148591</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,64%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43597</t>
+          <t>44412</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62582</t>
+          <t>62847</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52512</t>
+          <t>53042</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76280</t>
+          <t>77217</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101238</t>
+          <t>101863</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>132441</t>
+          <t>133079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,98%</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42241</t>
+          <t>42782</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28009</t>
+          <t>27555</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28282</t>
+          <t>27961</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63413</t>
+          <t>61894</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>110382</t>
+          <t>108888</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>147303</t>
+          <t>146384</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>142360</t>
+          <t>141959</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>200330</t>
+          <t>195018</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>262252</t>
+          <t>263413</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>329584</t>
+          <t>329076</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>236572</t>
+          <t>235360</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>299477</t>
+          <t>296478</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>309217</t>
+          <t>308951</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>367424</t>
+          <t>365508</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>559461</t>
+          <t>565800</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>644906</t>
+          <t>647219</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>215004</t>
+          <t>213635</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>301403</t>
+          <t>298532</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>216796</t>
+          <t>216137</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>270262</t>
+          <t>268832</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>444803</t>
+          <t>444795</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>547241</t>
+          <t>541481</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
